--- a/data/trans_orig/IP07KS_C07_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C07_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de trato justo por parte de sus padres en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de trato justo por parte de sus padres, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,69 +725,69 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>657</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>55,25%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>43,12%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>44,75%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>513</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39070</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26624</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45924</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>71,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>84,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>30909</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9207</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>56323</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>49,97%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41082</t>
+          <t>31745</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29454</t>
+          <t>23747</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48623</t>
+          <t>35671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>71991</t>
+          <t>70814</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34477</t>
+          <t>58965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97265</t>
+          <t>79987</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>86,13%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4059</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22354</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>18,28%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30948</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5534</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>52650</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>50,03%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>42191</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80927</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -1628,82 +1628,82 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1774</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7884</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>13,63%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -1854,107 +1854,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3761</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9025</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20248</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16955</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>21884</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>90,06%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>75,41%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>16753</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13048</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19381</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>80,28%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>62,52%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22345</t>
+          <t>16763</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24227</t>
+          <t>18966</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>39099</t>
+          <t>37011</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34009</t>
+          <t>32019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42344</t>
+          <t>40031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4019</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>17,87%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>4116</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1488</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7821</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,48%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10290</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -2310,82 +2310,82 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>955</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>6252</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>25,19%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>955</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>22484</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>22484</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>22484</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>24821</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24821</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24821</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>45690</t>
+          <t>43334</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45690</t>
+          <t>43334</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45690</t>
+          <t>43334</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,74 +2766,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>15936</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9192</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>91,42%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>52,74%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2211</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>83,48%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2575</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>87,64%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>25,95%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>18268</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>11241</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>19750</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>92,5%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>56,92%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -2841,27 +2841,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>20480</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2879,82 +2879,82 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1482</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>8509</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>43,08%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>88,96%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>363</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>363</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>15494</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>12170</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>17844</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>76,38%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>60,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>87,96%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>11745</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>8362</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>13543</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>79,91%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>56,89%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>92,14%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17593</t>
+          <t>14458</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>28022</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22615</t>
+          <t>23319</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30084</t>
+          <t>31153</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,88%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -3674,82 +3674,82 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>571</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>571</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -3787,82 +3787,82 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>3983</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>5,79%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>19,93%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,74 +4130,74 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>15464</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>11109</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>17885</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>79,5%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>57,11%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>91,95%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>17457</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>15328</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>83,19%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>18294</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>15661</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>19363</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>80,88%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>16877</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>11665</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>19575</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>80,6%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>55,71%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>93,48%</t>
-        </is>
-      </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>54</t>
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>34335</t>
+          <t>33759</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>27819</t>
+          <t>28204</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>37455</t>
+          <t>36644</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>3412</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>7965</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>17,54%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>40,95%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>3097</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>9747</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -4356,82 +4356,82 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>3377</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>16,13%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>574</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>41156</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>36060</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>44968</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>86,54%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>75,82%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>94,55%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>21738</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>17488</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>25038</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>79,64%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>64,07%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>91,73%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>39950</t>
+          <t>22896</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>34256</t>
+          <t>17639</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>43459</t>
+          <t>26130</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>61688</t>
+          <t>64052</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>54587</t>
+          <t>57635</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>66808</t>
+          <t>69381</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>5543</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>11096</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>23,33%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>3678</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>8060</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>13,47%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>29,53%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>15618</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>1879</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>4977</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>344</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>350</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -5264,82 +5264,82 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>859</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>797</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>4283</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>859</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,72 +5494,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>25691</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>18508</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>34997</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>21,21%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>40,11%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>18488</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>12717</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>25189</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>29,11%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>39,67%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>20177</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>16358</t>
+          <t>13823</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>31337</t>
+          <t>27612</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>41988</t>
+          <t>45869</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>35791</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>51962</t>
+          <t>57008</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -5607,107 +5607,107 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>54064</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>44852</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>62532</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>61,97%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>51,41%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>71,67%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>39773</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>32786</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>46299</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>62,63%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>51,63%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>72,91%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>50747</t>
+          <t>44313</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>37241</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>59131</t>
+          <t>51078</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
+          <t>62,95%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>52,9%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>72,56%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>98377</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>86726</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>109603</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
           <t>62,41%</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>52,93%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>72,72%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>90519</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>79405</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>101048</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>62,51%</t>
-        </is>
-      </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -5720,72 +5720,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>7493</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>3141</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>14310</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>16,4%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>4799</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>9652</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>15,2%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>13011</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>18526</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -5946,72 +5946,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>2363</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>385</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>385</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6176,72 +6176,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>173717</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>158483</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>190640</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>64,46%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>58,81%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>70,74%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>119971</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>77142</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>142857</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>57,0%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>36,65%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>67,87%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>177968</t>
+          <t>125611</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>160102</t>
+          <t>112461</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>196191</t>
+          <t>137135</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>297939</t>
+          <t>299328</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>244150</t>
+          <t>278565</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>323177</t>
+          <t>319241</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -6289,72 +6289,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>78774</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>62124</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>94734</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>29,23%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>23,05%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>35,15%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>82942</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>59446</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>128532</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>61,07%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>76700</t>
+          <t>63767</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>60352</t>
+          <t>52548</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>92616</t>
+          <t>76563</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>159642</t>
+          <t>142542</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>131933</t>
+          <t>124656</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>215864</t>
+          <t>162755</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -6402,72 +6402,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>11247</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>5942</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>19873</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>6678</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>3019</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>13389</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>19458</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>27153</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -6515,82 +6515,82 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>3660</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -6628,72 +6628,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>4580</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>9660</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>881</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>2735</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>748</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>10860</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11142</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>269506</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>269506</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>269506</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>271551</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>271551</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>271551</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>467094</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>467094</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>467094</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
